--- a/data/interm/ESPAÑA merge intermedio 2.xlsx
+++ b/data/interm/ESPAÑA merge intermedio 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoriadiesanchez/Documents/UFV/CURSO 4/TFG/NUEVO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54351F02-95C3-1F43-BAFB-7254F758EC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E30CCF6-EE2D-4645-A5C5-849B0D850D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="5" activeTab="12" xr2:uid="{ABE133A8-5FA3-3241-8560-7F810F1958BC}"/>
   </bookViews>
@@ -2100,6 +2100,10 @@
       <c r="C9">
         <v>74.69</v>
       </c>
+      <c r="D9">
+        <f>FORECAST(Tabla18[[#This Row],[YEAR]],D11:D13,A11:A13)</f>
+        <v>34.700000000000045</v>
+      </c>
       <c r="E9">
         <v>459</v>
       </c>
@@ -2147,6 +2151,10 @@
       </c>
       <c r="C10">
         <v>75.28</v>
+      </c>
+      <c r="D10">
+        <f>FORECAST(Tabla18[[#This Row],[YEAR]],D11:D13,A11:A13)</f>
+        <v>34.525000000000034</v>
       </c>
       <c r="E10">
         <v>434</v>
